--- a/stories/arbres/TREE-SAN-076.xlsx
+++ b/stories/arbres/TREE-SAN-076.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Lila est avec papa, près de la fenêtre. Lila a envie de jouer. papa est là, tout près. On va apprendre : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila écoute papa. Lila entend les mots : mouchoir, poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le bac à sable. Un vélo passe au loin. papa sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On range un objet. papa dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers le bac à sable. Un vélo passe au loin. papa sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers le bac à sable. Un vélo passe au loin. papa sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On range un objet.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Se moucher.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre un mouchoir ; jeter. Lila respire. Lila retient : mouchoir, poubelle. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2230,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2397,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2541,6 +2594,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2705,6 +2763,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. La couverture est douce. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2867,6 +2930,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3029,6 +3097,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3191,6 +3264,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3353,6 +3431,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3515,6 +3598,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3677,6 +3765,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3869,6 +3962,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4033,6 +4131,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. On entend un oiseau. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4195,6 +4298,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4357,6 +4465,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4519,6 +4632,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4681,6 +4799,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4843,6 +4966,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5005,6 +5133,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5197,6 +5330,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5361,6 +5499,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5523,6 +5666,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5685,6 +5833,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5847,6 +6000,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6009,6 +6167,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6171,6 +6334,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6195,7 +6363,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le toboggan. La lumière est claire. papa sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On dit merci. papa dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers le toboggan. La lumière est claire. papa sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6333,6 +6501,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers le toboggan. La lumière est claire. papa sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On dit merci.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6509,6 +6683,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Se moucher.</t>
         </is>
       </c>
     </row>
@@ -6677,6 +6856,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre un mouchoir ; jeter. Lila respire. Lila retient : mouchoir, poubelle. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6867,6 +7051,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7029,6 +7218,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7221,6 +7415,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7385,6 +7584,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7547,6 +7751,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7709,6 +7918,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7871,6 +8085,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8033,6 +8252,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8195,6 +8419,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8357,6 +8586,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8549,6 +8783,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8713,6 +8952,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8875,6 +9119,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9037,6 +9286,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9199,6 +9453,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9361,6 +9620,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9523,6 +9787,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9685,6 +9954,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9877,6 +10151,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10041,6 +10320,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10203,6 +10487,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10365,6 +10654,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10527,6 +10821,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10689,6 +10988,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10851,6 +11155,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10875,7 +11184,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers les balançoires. Il y a des miettes sur la table. papa sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On souffle doucement. papa dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers les balançoires. Il y a des miettes sur la table. papa sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11013,6 +11322,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers les balançoires. Il y a des miettes sur la table. papa sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On souffle doucement.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11189,6 +11504,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Se moucher.</t>
         </is>
       </c>
     </row>
@@ -11357,6 +11677,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre un mouchoir ; jeter. Lila respire. Lila retient : mouchoir, poubelle. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11547,6 +11872,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11709,6 +12039,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11901,6 +12236,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12065,6 +12405,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12227,6 +12572,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12389,6 +12739,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12551,6 +12906,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12713,6 +13073,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12875,6 +13240,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13037,6 +13407,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13229,6 +13604,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13393,6 +13773,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13555,6 +13940,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13717,6 +14107,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13879,6 +14274,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14041,6 +14441,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14203,6 +14608,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14365,6 +14775,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14557,6 +14972,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14721,6 +15141,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14883,6 +15308,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15045,6 +15475,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15207,6 +15642,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15369,6 +15809,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15531,6 +15976,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15549,7 +15999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15622,6 +16072,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-076.xlsx
+++ b/stories/arbres/TREE-SAN-076.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Lila est avec papa, près de la fenêtre. Lila a envie de jouer. papa est là, tout près. On va apprendre : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila écoute papa. Lila entend les mots : mouchoir, poubelle.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Se moucher.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : prendre un mouchoir ; jeter. Lila respire. Lila retient : mouchoir, poubelle. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2235,6 +2245,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2402,6 +2413,7 @@
           <t>narrateur|Lila a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2601,6 +2613,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2768,6 +2781,7 @@
           <t>narrateur|Lila rejoint Tom. La couverture est douce. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2935,6 +2949,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3102,6 +3117,7 @@
           <t>narrateur|Lila rejoint Léa. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3269,6 +3285,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3436,6 +3453,7 @@
           <t>narrateur|Lila rejoint Sami. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3603,6 +3621,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3770,6 +3789,7 @@
           <t>narrateur|Lila a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3969,6 +3989,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4136,6 +4157,7 @@
           <t>narrateur|Lila rejoint Tom. On entend un oiseau. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4303,6 +4325,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4470,6 +4493,7 @@
           <t>narrateur|Lila rejoint Léa. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4637,6 +4661,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4804,6 +4829,7 @@
           <t>narrateur|Lila rejoint Sami. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4971,6 +4997,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5138,6 +5165,7 @@
           <t>narrateur|Lila a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5337,6 +5365,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5504,6 +5533,7 @@
           <t>narrateur|Lila rejoint Tom. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5671,6 +5701,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5838,6 +5869,7 @@
           <t>narrateur|Lila rejoint Léa. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6005,6 +6037,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6172,6 +6205,7 @@
           <t>narrateur|Lila rejoint Sami. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6339,6 +6373,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6507,6 +6542,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6690,6 +6726,7 @@
           <t>narrateur|Que fait-on ? Se moucher.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6861,6 +6898,7 @@
           <t>narrateur|Oui. Voici le geste : prendre un mouchoir ; jeter. Lila respire. Lila retient : mouchoir, poubelle. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7056,6 +7094,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7223,6 +7262,7 @@
           <t>narrateur|Lila a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7422,6 +7462,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7589,6 +7630,7 @@
           <t>narrateur|Lila rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7756,6 +7798,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7923,6 +7966,7 @@
           <t>narrateur|Lila rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8090,6 +8134,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8257,6 +8302,7 @@
           <t>narrateur|Lila rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8424,6 +8470,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8591,6 +8638,7 @@
           <t>narrateur|Lila a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8790,6 +8838,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8957,6 +9006,7 @@
           <t>narrateur|Lila rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9124,6 +9174,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9291,6 +9342,7 @@
           <t>narrateur|Lila rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9458,6 +9510,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9625,6 +9678,7 @@
           <t>narrateur|Lila rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9792,6 +9846,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9959,6 +10014,7 @@
           <t>narrateur|Lila a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10158,6 +10214,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10325,6 +10382,7 @@
           <t>narrateur|Lila rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10492,6 +10550,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10659,6 +10718,7 @@
           <t>narrateur|Lila rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10826,6 +10886,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10993,6 +11054,7 @@
           <t>narrateur|Lila rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11160,6 +11222,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11328,6 +11391,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11511,6 +11575,7 @@
           <t>narrateur|Que fait-on ? Se moucher.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11682,6 +11747,7 @@
           <t>narrateur|Oui. Voici le geste : prendre un mouchoir ; jeter. Lila respire. Lila retient : mouchoir, poubelle. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11877,6 +11943,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12044,6 +12111,7 @@
           <t>narrateur|Lila a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12243,6 +12311,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12410,6 +12479,7 @@
           <t>narrateur|Lila rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12577,6 +12647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12744,6 +12815,7 @@
           <t>narrateur|Lila rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12911,6 +12983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13078,6 +13151,7 @@
           <t>narrateur|Lila rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13245,6 +13319,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13412,6 +13487,7 @@
           <t>narrateur|Lila a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13611,6 +13687,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13778,6 +13855,7 @@
           <t>narrateur|Lila rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13945,6 +14023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14112,6 +14191,7 @@
           <t>narrateur|Lila rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14279,6 +14359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14446,6 +14527,7 @@
           <t>narrateur|Lila rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14613,6 +14695,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14780,6 +14863,7 @@
           <t>narrateur|Lila a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Lila répète tout bas : mouchoir, poubelle. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14979,6 +15063,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15146,6 +15231,7 @@
           <t>narrateur|Lila rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15313,6 +15399,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15480,6 +15567,7 @@
           <t>narrateur|Lila rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15647,6 +15735,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15814,6 +15903,7 @@
           <t>narrateur|Lila rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Lila a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Lila a entendu : mouchoir, poubelle. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15981,6 +16071,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15999,7 +16090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16079,6 +16170,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16093,7 +16198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16280,6 +16385,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
